--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>77937.53</v>
+        <v>79052.75</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>41135.32</v>
+        <v>41723.93</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>38545.06</v>
+        <v>38997.21</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>37182.55</v>
+        <v>37618.72</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>36838.4</v>
+        <v>37270.54</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>18247.8</v>
+        <v>18461.86</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>77967.7</v>
+        <v>78882.3</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>69895.17</v>
+        <v>70715.08</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>34762.19</v>
+        <v>35169.97</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>39425.33</v>
+        <v>40092.11</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>23470.22</v>
+        <v>23867.16</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>19031.32</v>
+        <v>19209.82</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>69364.61</v>
+        <v>70015.2</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>14167.34</v>
+        <v>14059.86</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>44633.81</v>
+        <v>44295.21</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>38968.76</v>
+        <v>38673.14</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>22138.97</v>
+        <v>21971.02</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>52246.83</v>
+        <v>51364.08</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>27437.64</v>
+        <v>26974.06</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>34997.99</v>
+        <v>34406.67</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>72186.33</v>
+        <v>71161.84</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>61945.41</v>
+        <v>61066.26</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>41135.32</v>
+        <v>40551.51</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>14154.85</v>
+        <v>13953.96</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>14247.32</v>
+        <v>14045.11</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>27078.35</v>
+        <v>26694.05</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>72690.97</v>
+        <v>71659.32000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>54523.08</v>
+        <v>53773.91</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>22987.66</v>
+        <v>22671.8</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>18297.73</v>
+        <v>18046.32</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>78885.42999999999</v>
+        <v>77801.52</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>25439.45</v>
+        <v>25089.9</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>29496.28</v>
+        <v>29091</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>67725.33</v>
+        <v>66794.75999999999</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>32364.52</v>
+        <v>32163.87</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>42669.29</v>
+        <v>42404.75</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>70315.81</v>
+        <v>70635.16</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>64607.72</v>
+        <v>64901.15</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>49632.37</v>
+        <v>50371.41</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>36766.29</v>
+        <v>37465.27</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>17771.27</v>
+        <v>18109.13</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>42741.95</v>
+        <v>43554.54</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>22297.04</v>
+        <v>22799.9</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>28194.2</v>
+        <v>28388.86</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>61996.23</v>
+        <v>62187.89</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>29634.47</v>
+        <v>29726.08</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>32616.1</v>
+        <v>32716.94</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>39122.88</v>
+        <v>39243.84</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>14647.21</v>
+        <v>14692.49</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>73294.95</v>
+        <v>73521.55</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>30235.3</v>
+        <v>30155.34</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>45103.17</v>
+        <v>44983.88</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>31415.2</v>
+        <v>31332.11</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>603.08</v>
+        <v>601.49</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>27885.14</v>
+        <v>27811.39</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>29744.15</v>
+        <v>29347.95</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>754.45</v>
+        <v>744.4</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>40571.88</v>
+        <v>40031.46</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>30100.91</v>
+        <v>29511.72</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1249.55</v>
+        <v>1225.1</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>37925.49</v>
+        <v>37183.14</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>16182.26</v>
+        <v>15865.51</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>33840.08</v>
+        <v>33338.71</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>11800.4</v>
+        <v>11625.57</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>396.28</v>
+        <v>390.41</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>25477.3</v>
+        <v>25099.83</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1444</v>
+        <v>1422.6</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>33208.46</v>
+        <v>32525.97</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>48407.97</v>
+        <v>47413.1</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>78885.42999999999</v>
+        <v>77264.2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Fresia - Salud</t>
+          <t>I MUNICIPALIDAD DE FRESIA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Santa Barbara - Salud</t>
+          <t>I MUNICIPALIDAD DE SANTA BARBARA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3320,7 +3320,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2404-799-CM26</t>
+          <t>3515-285-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,27 +3345,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PILMAIQUEN SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.262.067-5</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>32716.94</v>
+        <v>39243.84</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3515-285-CM26</t>
+          <t>3887-225-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3406,27 +3406,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>39243.84</v>
+        <v>14692.49</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3887-225-CM26</t>
+          <t>3416-328-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3462,32 +3462,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.101.017-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>14692.49</v>
+        <v>73521.55</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3416-328-CM26</t>
+          <t>642028-37-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.101.017-6</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>73521.55</v>
+        <v>30155.34</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>642028-37-CM26</t>
+          <t>2337-57-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3584,32 +3584,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>30155.34</v>
+        <v>31332.11</v>
       </c>
     </row>
     <row r="53">
@@ -3686,7 +3686,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2337-57-CM26</t>
+          <t>2345-260-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3711,27 +3711,27 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>31332.11</v>
+        <v>27811.39</v>
       </c>
     </row>
     <row r="55">
@@ -3808,7 +3808,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2345-260-CM26</t>
+          <t>2429-733-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,37 +3823,37 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>27811.39</v>
+        <v>29347.95</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2429-733-CM26</t>
+          <t>2429-734-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>29347.95</v>
+        <v>744.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2429-734-CM26</t>
+          <t>2963-69-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3955,27 +3955,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.072.400-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE LA GRANJA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>744.4</v>
+        <v>40031.46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2963-69-CM26</t>
+          <t>1426095-156-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,27 +4016,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.072.400-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>40031.46</v>
+        <v>1225.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1426095-155-CM26</t>
+          <t>2322-454-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4072,22 +4072,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>29511.72</v>
+        <v>37183.14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1426095-156-CM26</t>
+          <t>2322-455-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,27 +4138,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1225.1</v>
+        <v>15865.51</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2322-454-CM26</t>
+          <t>1426095-155-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4199,17 +4199,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>37183.14</v>
+        <v>29511.72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2322-455-CM26</t>
+          <t>941739-50-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,27 +4260,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>15865.51</v>
+        <v>33338.71</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>941739-50-CM26</t>
+          <t>3661-357-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4316,32 +4316,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>33338.71</v>
+        <v>11625.57</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3661-357-CM26</t>
+          <t>3661-358-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>11625.57</v>
+        <v>390.41</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3661-358-CM26</t>
+          <t>1456836-6-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4443,27 +4443,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>61.981.410-K</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>390.41</v>
+        <v>25099.83</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1456836-6-CM26</t>
+          <t>1456836-7-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>25099.83</v>
+        <v>1422.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1456836-7-CM26</t>
+          <t>4314-256-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,27 +4565,27 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.981.410-K</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1422.6</v>
+        <v>32525.97</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4314-256-CM26</t>
+          <t>1180825-16-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4621,32 +4621,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>32525.97</v>
+        <v>47413.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1180825-16-CM26</t>
+          <t>1286987-18-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4682,32 +4682,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>65.797.310-6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>Corporación Municipal de Deportes y Recreación Coyhaique</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,67 +4717,6 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>47413.1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>1286987-18-CM26</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>65.797.310-6</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Corporación Municipal de Deportes y Recreación Coy</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="n">
         <v>77264.2</v>
       </c>
     </row>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
@@ -562,7 +562,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1261,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1387,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1513,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1578,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1826,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1891,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1956,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2082,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2147,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2212,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2277,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2403,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2468,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2533,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2598,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2785,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2850,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2976,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3102,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3228,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3293,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3358,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3423,11 @@
           <t>78.027.627-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3488,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3675,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3740,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3805,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3870,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3935,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4000,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4065,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4191,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4256,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4382,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4630,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4695,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4760,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4825,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4890,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
@@ -4447,7 +4447,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2026.xlsx
@@ -1424,7 +1424,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
